--- a/data/trans_dic/IP21B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,05</t>
+          <t>0,0; 63,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,47</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,21</t>
+          <t>0,0; 56,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,77</t>
+          <t>0,0; 45,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,25</t>
+          <t>0,0; 56,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,31</t>
+          <t>0,0; 44,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,96</t>
+          <t>0,0; 25,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,15</t>
+          <t>0,0; 40,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,27</t>
+          <t>0,0; 46,61</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,65</t>
+          <t>0,0; 32,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 51,93</t>
+          <t>6,66; 52,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 55,25</t>
+          <t>6,83; 55,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,55</t>
+          <t>0,0; 39,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,16</t>
+          <t>0,0; 50,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,56</t>
+          <t>0,0; 51,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,7</t>
+          <t>0,0; 79,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 25,16</t>
+          <t>3,07; 26,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 42,45</t>
+          <t>11,48; 42,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 43,68</t>
+          <t>7,53; 42,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,85</t>
+          <t>0,0; 57,57</t>
         </is>
       </c>
     </row>
@@ -996,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,28</t>
+          <t>0,0; 78,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,82</t>
+          <t>0,0; 39,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 41,79</t>
+          <t>5,93; 45,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1036,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,11</t>
+          <t>0,0; 25,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 29,63</t>
+          <t>2,06; 29,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,17</t>
+          <t>0,0; 64,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,28</t>
+          <t>0,0; 78,15</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,8</t>
+          <t>0,0; 78,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,03</t>
+          <t>0,0; 50,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 85,15</t>
+          <t>12,48; 85,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,78</t>
+          <t>0,0; 37,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 51,66</t>
+          <t>6,6; 48,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,98</t>
+          <t>0,0; 80,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 37,36</t>
+          <t>4,23; 36,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 40,71</t>
+          <t>7,85; 41,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 56,33</t>
+          <t>7,33; 57,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,58</t>
+          <t>0,0; 72,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 21,69</t>
+          <t>2,68; 22,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 30,07</t>
+          <t>5,95; 30,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 39,94</t>
+          <t>9,79; 39,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 51,97</t>
+          <t>6,65; 52,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 22,93</t>
+          <t>4,41; 24,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 31,21</t>
+          <t>9,24; 30,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 40,87</t>
+          <t>9,39; 41,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 54,06</t>
+          <t>6,14; 52,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 19,07</t>
+          <t>5,67; 19,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 25,26</t>
+          <t>9,56; 25,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 33,65</t>
+          <t>12,76; 33,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 43,04</t>
+          <t>12,21; 45,42</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2446</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1993</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2986</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3128</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3842</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4060</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2821</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4304</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2384</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3996</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3612</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>699; 5530</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>621; 5066</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3851</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3321</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3088</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3819</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>641; 5531</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1966; 7359</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1135; 6433</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3870</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3545</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2890</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>580; 4421</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2965</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3549</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>308; 4486</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3883</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3545</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3641</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2942</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4123</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>645; 4409</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3999</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>604; 4476</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2838</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3663</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>613; 5282</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1364; 7227</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>744; 5854</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3837</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9171</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>681; 5737</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1669; 8673</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2078; 8339</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>613; 4824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1462; 8152</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3001; 9808</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1944; 8486</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>765; 6519</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3318; 11486</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5781; 15126</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5348; 14049</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2647; 9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Habitat-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,36</t>
+          <t>0,0; 63,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,22 +732,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 83,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,67</t>
+          <t>0,0; 68,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,18</t>
+          <t>0,0; 45,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,9</t>
+          <t>0,0; 57,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,48</t>
+          <t>0,0; 44,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,55</t>
+          <t>0,0; 26,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,21</t>
+          <t>0,0; 36,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,61</t>
+          <t>0,0; 55,42</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,52</t>
+          <t>0,0; 35,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 52,66</t>
+          <t>6,54; 51,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 55,74</t>
+          <t>8,34; 56,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,54</t>
+          <t>0,0; 40,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,11</t>
+          <t>0,0; 59,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,54</t>
+          <t>0,0; 49,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,98</t>
+          <t>0,0; 78,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 26,53</t>
+          <t>3,14; 27,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 42,96</t>
+          <t>11,42; 42,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 42,66</t>
+          <t>8,02; 45,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,57</t>
+          <t>0,0; 61,96</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,15</t>
+          <t>0,0; 78,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,19</t>
+          <t>0,0; 38,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 45,22</t>
+          <t>5,87; 45,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,21</t>
+          <t>0,0; 30,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 29,98</t>
+          <t>3,8; 33,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,85</t>
+          <t>0,0; 62,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,15</t>
+          <t>0,0; 78,14</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,71</t>
+          <t>0,0; 78,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,15</t>
+          <t>0,0; 56,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 85,36</t>
+          <t>12,77; 81,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,13</t>
+          <t>0,0; 36,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 48,93</t>
+          <t>6,19; 51,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,88</t>
+          <t>0,0; 57,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,27</t>
+          <t>0,0; 80,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 36,4</t>
+          <t>4,19; 32,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 41,61</t>
+          <t>7,55; 40,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 57,65</t>
+          <t>7,11; 55,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,37</t>
+          <t>0,0; 73,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,58</t>
+          <t>2,29; 20,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 30,95</t>
+          <t>5,56; 29,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 39,28</t>
+          <t>10,16; 40,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 52,35</t>
+          <t>6,65; 51,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,59</t>
+          <t>5,66; 22,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,2</t>
+          <t>8,27; 30,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,0</t>
+          <t>7,71; 39,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,31</t>
+          <t>7,29; 55,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 19,61</t>
+          <t>5,66; 18,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 25,0</t>
+          <t>9,62; 25,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 33,51</t>
+          <t>12,56; 33,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 45,42</t>
+          <t>11,03; 45,71</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2446</t>
+          <t>0; 2444</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>0; 1664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2986</t>
+          <t>0; 3587</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>0; 3120</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4060</t>
+          <t>0; 4073</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2821</t>
+          <t>0; 2960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4304</t>
+          <t>0; 3880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2384</t>
+          <t>0; 2835</t>
         </is>
       </c>
     </row>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3919</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>699; 5530</t>
+          <t>687; 5388</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>621; 5066</t>
+          <t>758; 5129</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,42 +1873,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3851</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3321</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 2993</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3819</t>
+          <t>0; 3765</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>641; 5531</t>
+          <t>655; 5642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1966; 7359</t>
+          <t>1956; 7323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1135; 6433</t>
+          <t>1209; 6807</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3870</t>
+          <t>0; 4165</t>
         </is>
       </c>
     </row>
@@ -2076,17 +2076,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>0; 3544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2890</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>580; 4421</t>
+          <t>574; 4403</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>0; 4233</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>308; 4486</t>
+          <t>568; 5015</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3883</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>0; 3544</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4123</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645; 4409</t>
+          <t>660; 4234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2289,42 +2289,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>0; 3933</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>604; 4476</t>
+          <t>566; 4722</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2838</t>
+          <t>0; 2881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3663</t>
+          <t>0; 3662</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>613; 5282</t>
+          <t>609; 4760</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1364; 7227</t>
+          <t>1312; 7020</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744; 5854</t>
+          <t>722; 5676</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3837</t>
+          <t>0; 3892</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>681; 5737</t>
+          <t>583; 5282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1669; 8673</t>
+          <t>1559; 8175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2078; 8339</t>
+          <t>2157; 8692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>613; 4824</t>
+          <t>613; 4782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1462; 8152</t>
+          <t>1877; 7536</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3001; 9808</t>
+          <t>2687; 9777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1944; 8486</t>
+          <t>1597; 8186</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>765; 6519</t>
+          <t>908; 6874</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3318; 11486</t>
+          <t>3316; 11013</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5781; 15126</t>
+          <t>5821; 15389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5348; 14049</t>
+          <t>5266; 14230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2647; 9845</t>
+          <t>2390; 9907</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>14,93%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,31</t>
+          <t>0,0; 57,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 42,77</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 58,25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 64,05</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 83,47</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 68,09</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 45,05</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 87,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,62</t>
+          <t>0,0; 39,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,82</t>
+          <t>0,0; 26,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,25</t>
+          <t>0,0; 36,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,42</t>
+          <t>0,0; 52,04</t>
         </is>
       </c>
     </row>
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>25,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>28,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11,94%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,29</t>
+          <t>0,0; 40,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 51,3</t>
+          <t>0,0; 50,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 56,44</t>
+          <t>0,0; 61,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 81,84</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 34,65</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,51; 51,93</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,47; 55,25</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 40,1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 59,49</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,96</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 78,85</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 27,06</t>
+          <t>3,06; 25,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 42,75</t>
+          <t>8,04; 42,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 45,14</t>
+          <t>8,67; 43,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,96</t>
+          <t>0,0; 60,04</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48,57%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>48,57%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 38,82</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5,9; 41,79</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 78,14</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 38,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,87; 45,04</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 84,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,06</t>
+          <t>0,0; 26,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 33,51</t>
+          <t>3,88; 29,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,32</t>
+          <t>0,0; 61,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,14</t>
+          <t>0,0; 84,71</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,06%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>42,65%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13,97%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,76</t>
+          <t>0,0; 36,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,02</t>
+          <t>5,87; 51,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 81,98</t>
+          <t>0,0; 56,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 80,43</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 78,8</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 56,03</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,87; 85,15</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,51</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,19; 51,62</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 57,74</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 80,26</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 32,81</t>
+          <t>4,28; 37,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 40,42</t>
+          <t>7,58; 40,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 55,89</t>
+          <t>6,99; 56,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,4</t>
+          <t>0,0; 73,52</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 20,79</t>
+          <t>4,29; 22,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 29,17</t>
+          <t>8,1; 31,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 40,95</t>
+          <t>7,93; 40,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 51,89</t>
+          <t>7,75; 55,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,73</t>
+          <t>2,51; 21,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 30,1</t>
+          <t>5,22; 30,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 39,55</t>
+          <t>9,84; 39,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 55,16</t>
+          <t>7,54; 55,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,81</t>
+          <t>5,38; 19,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 25,44</t>
+          <t>9,75; 25,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 33,94</t>
+          <t>12,2; 33,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 45,71</t>
+          <t>11,63; 44,95</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>576</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1494</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>627</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2444</t>
+          <t>0; 3014</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 2962</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2472</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1664</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3587</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3120</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1688</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4073</t>
+          <t>0; 3588</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>0; 2976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3880</t>
+          <t>0; 3870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2835</t>
+          <t>0; 2396</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,44 +1785,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2696</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2575</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1430</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2489</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1363</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3919</t>
+          <t>0; 3949</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>687; 5388</t>
+          <t>0; 3324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>758; 5129</t>
+          <t>0; 3688</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0; 3704</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3848</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>683; 5453</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>770; 5021</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3905</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3943</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2993</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3765</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>655; 5642</t>
+          <t>638; 5245</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1956; 7323</t>
+          <t>1378; 7271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1209; 6807</t>
+          <t>1307; 6586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4165</t>
+          <t>0; 3796</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>1888</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>1440</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1888</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1730</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 2863</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>577; 4085</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2965</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3544</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2855</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>574; 4403</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2965</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3742</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4233</t>
+          <t>0; 3676</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>568; 5015</t>
+          <t>581; 4434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3544</t>
+          <t>0; 3742</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,44 +2201,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1657</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2203</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2028</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1636</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2944</t>
+          <t>0; 3962</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>537; 4726</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2838</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3310</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2946</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>0; 4606</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>660; 4234</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>665; 4398</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3933</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>566; 4722</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2881</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3662</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>609; 4760</t>
+          <t>622; 5420</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1312; 7020</t>
+          <t>1316; 7071</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>722; 5676</t>
+          <t>710; 5720</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3892</t>
+          <t>0; 3541</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>583; 5282</t>
+          <t>1421; 7603</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1559; 8175</t>
+          <t>2630; 10136</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2157; 8692</t>
+          <t>1642; 8458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>613; 4782</t>
+          <t>877; 6332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1877; 7536</t>
+          <t>638; 5511</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2687; 9777</t>
+          <t>1463; 8427</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1597; 8186</t>
+          <t>2089; 8479</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>908; 6874</t>
+          <t>666; 4896</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3316; 11013</t>
+          <t>3148; 11170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5821; 15389</t>
+          <t>5902; 15280</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5266; 14230</t>
+          <t>5116; 14107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2390; 9907</t>
+          <t>2344; 9061</t>
         </is>
       </c>
     </row>
